--- a/data.mn/public/datasets/meat-production-total-mn.xlsx
+++ b/data.mn/public/datasets/meat-production-total-mn.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,20 +413,16 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="17" customWidth="1" min="2" max="2"/>
-  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" t="inlineStr">
         <is>
           <t>он</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" t="inlineStr">
         <is>
           <t>үйлдвэрлэл_тонн</t>
         </is>
@@ -521,7 +505,7 @@
         <v>2019</v>
       </c>
       <c r="B11" t="n">
-        <v>545029.2</v>
+        <v>543817.1</v>
       </c>
     </row>
     <row r="12">
@@ -529,7 +513,7 @@
         <v>2020</v>
       </c>
       <c r="B12" t="n">
-        <v>744516</v>
+        <v>746161.1</v>
       </c>
     </row>
     <row r="13">
@@ -537,7 +521,7 @@
         <v>2021</v>
       </c>
       <c r="B13" t="n">
-        <v>512679.2</v>
+        <v>506970.2</v>
       </c>
     </row>
     <row r="14">
@@ -545,7 +529,7 @@
         <v>2022</v>
       </c>
       <c r="B14" t="n">
-        <v>653966.6</v>
+        <v>650145.9</v>
       </c>
     </row>
     <row r="15">
@@ -553,7 +537,7 @@
         <v>2023</v>
       </c>
       <c r="B15" t="n">
-        <v>622082.7</v>
+        <v>668559.2</v>
       </c>
     </row>
     <row r="16">
@@ -561,7 +545,15 @@
         <v>2024</v>
       </c>
       <c r="B16" t="n">
-        <v>450443.1</v>
+        <v>453136.6</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2025</v>
+      </c>
+      <c r="B17" t="n">
+        <v>699872.382</v>
       </c>
     </row>
   </sheetData>
